--- a/Cuadro 40 - Representante  Proclamados Parciales_2014_DESBLOQ.xlsx
+++ b/Cuadro 40 - Representante  Proclamados Parciales_2014_DESBLOQ.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="20417"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\eacastillo\Desktop\PROYECTO DASHBOARD\PARA DASHBOARD\REPRESENTANTES DESBLOQ\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/a6047084e474bb5d/Desktop/PROYECTO DASHBOARD/EJECUCION_DASHBOARD_REPRES/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5DDE93ED-FCC0-48AF-A40C-CBD22DD50C3A}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="13_ncr:1_{5DDE93ED-FCC0-48AF-A40C-CBD22DD50C3A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4874D1B1-C76A-42A0-ADC6-29CC966491F4}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="900" windowWidth="28800" windowHeight="12360" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11760" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="repre2014_parciales" sheetId="1" r:id="rId1"/>
@@ -180,20 +180,19 @@
   <cellStyleXfs count="1">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+  <cellXfs count="6">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -211,10 +210,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<x18tc:personList xmlns:x18tc="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments"/>
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -432,174 +427,173 @@
   <dimension ref="A1:E11"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="12.625" defaultRowHeight="12" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="1" width="56.5" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.25" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="18.375" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="28.875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="18.25" style="1" customWidth="1"/>
-    <col min="6" max="23" width="9.5" style="1" customWidth="1"/>
-    <col min="24" max="16384" width="12.625" style="1"/>
+    <col min="1" max="1" width="13.5" customWidth="1"/>
+    <col min="2" max="2" width="12.25" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="18.375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="28.875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="18.25" customWidth="1"/>
+    <col min="6" max="23" width="9.5" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A1" s="3" t="s">
+      <c r="A1" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="B1" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="C1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="D1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="E1" s="2" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A2" s="4" t="s">
+      <c r="A2" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="4" t="s">
+      <c r="B2" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="C2" s="4" t="s">
+      <c r="C2" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="D2" s="5" t="s">
+      <c r="D2" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="6" t="s">
+      <c r="E2" s="5" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A3" s="4" t="s">
+      <c r="A3" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="B3" s="4" t="s">
+      <c r="B3" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="C3" s="4" t="s">
+      <c r="C3" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="D3" s="5" t="s">
+      <c r="D3" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="E3" s="6" t="s">
+      <c r="E3" s="5" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A4" s="4" t="s">
+      <c r="A4" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="B4" s="4" t="s">
+      <c r="B4" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="C4" s="4" t="s">
+      <c r="C4" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="D4" s="5" t="s">
+      <c r="D4" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="E4" s="6" t="s">
+      <c r="E4" s="5" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A5" s="4" t="s">
+      <c r="A5" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="B5" s="4" t="s">
+      <c r="B5" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="C5" s="4" t="s">
+      <c r="C5" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="D5" s="5" t="s">
+      <c r="D5" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="E5" s="6" t="s">
+      <c r="E5" s="5" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A6" s="4" t="s">
+      <c r="A6" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="B6" s="4" t="s">
+      <c r="B6" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="C6" s="4" t="s">
+      <c r="C6" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="D6" s="5" t="s">
+      <c r="D6" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="E6" s="6" t="s">
+      <c r="E6" s="5" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A7" s="4" t="s">
+      <c r="A7" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="B7" s="4" t="s">
+      <c r="B7" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="C7" s="4" t="s">
+      <c r="C7" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="D7" s="5" t="s">
+      <c r="D7" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="E7" s="6" t="s">
+      <c r="E7" s="5" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A8" s="4" t="s">
+      <c r="A8" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="B8" s="4" t="s">
+      <c r="B8" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="C8" s="4" t="s">
+      <c r="C8" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="D8" s="5" t="s">
+      <c r="D8" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="E8" s="6" t="s">
+      <c r="E8" s="5" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A9" s="4" t="s">
+      <c r="A9" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="B9" s="4" t="s">
+      <c r="B9" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="C9" s="4" t="s">
+      <c r="C9" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="D9" s="5" t="s">
+      <c r="D9" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="E9" s="6" t="s">
+      <c r="E9" s="5" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="11" spans="1:5" ht="15" x14ac:dyDescent="0.25">
-      <c r="A11" s="2" t="s">
+      <c r="A11" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="B11" s="2"/>
-      <c r="C11" s="2"/>
+      <c r="B11" s="1"/>
+      <c r="C11" s="1"/>
     </row>
   </sheetData>
   <printOptions horizontalCentered="1"/>
